--- a/vse-loti/339193000/spec-339193000.xlsx
+++ b/vse-loti/339193000/spec-339193000.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -497,13 +497,50 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>комплект со склада СОТ (шкаф, ИБП с картой мониторинга, АВР – новые на складе СОТ), смонтировать по проекту с переносом линий. Доукомплектовать шкаф «грозозацитой SNR-SPNet-PRM24-v2» и 3 модулями «Грозозащита Ethernet SNR-SPNet-BP1100», патч панелью ( cabeus 7955 c + 7962 c или аналог) (Приложение 2 ) . Видеокамеру CAM-66-ST подключить с использование POE удлинителя. POE удлинитель разместить в боксе, в доступном месте, на высоте 1,5 м. Предусмотреть доукомплектование узлов связи N узла ИБП (оборудование Заказчика) Грозозащита SNR-SPNet-PRM24-v2» и модули Ethernet SNR-SPNet-BP1100» (оборудование Подрядчика) Патч панель (cabeus 7955c + 7962c или аналог) (оборудование Подрядчика) N01 + N02 + + + N04 + + + N10 + + + Требования к архитектурно-строительным, объемно-планировочным и конструктивным решениям Не требуется Требования к режиму безопасности и гигиене труда Технические решения должны соответствовать требованиям экономических, санитарно-гигиенических, противопожарных и других норм, действующих на территории Российской Федерации, и обеспечивать безопасную для жизни и здоровья людей эксплуатацию объекта. Устанавливаемое на объекте оборудование должно быть безвредно для здоровья лиц, имеющих доступ на объект. Требования и условия для разработки природоохранных мер и мероприятий Не требуется . Требования по разработке инженерно-технических мероприятий по гражданской обороне и предупреждению чрезвычайных ситуаций Не требуется . Требования по выполнению исследований и конструкторских разработок Не требуется . Требования к проведению, оформлению и представлению расчета стоимости строительства Локально сметный расчет выполнить ресурсно-индексным методом в федеральной сметно-нормативной базе ФСНБ 2022 г. Для материалов отсутствующих в сметно-нормативной базе, в расчете предоставить конъюнктурный анализ с предоставлением не менее трех прайсов на каждую позицию материалов поставщиков Челябинской области. Особые условия Не требуются . Перечень технических регламентов и стандартов, норм и правил, соответствие которым необходимо обеспечить при проектировании ГОСТ Р 21.1101-20 20 СПДС. Основные требования к проектной и рабочей документации (с Поправкой) ГОСТ Р 21.101-2020 СПДС. Спецификация оборудования, изделий и материалов. ГОСТ Р 53246-2008 Информационные технологии (ИТ). Системы кабельные структурированные. Проектирование основных узлов системы. Общие требования. ГОСТ Р 53245-2008. Информационные технологии. Системы кабельные структурированные. Монтаж основных узлов системы. Методы испытания. Правила по охране труда при эксплуатации электроустановок Правила по охране труда при выполнении работ на объектах связи Перечень согласований и экспертиз в государственных федеральных и региональных надзорных органах Не требуется . Требования к процедуре подтверждения соответствия проекта Заданию на проектирование Внутренняя экспертиза Заказчика (ПСД и проектных решений) . Требования к телекоммуникационной инфраструктуре Для подключения проектируемого объекта к сети передачи данных запросить технические условия в управлении ИТ филиала ПАО «ТМК» ЧТПЗ на этапе проектирования. Проектирование и строительство объекта выполнить в соответствии с типовыми требованиями ИТ к телекоммуникационной инфраструктуре. (приложение 3 ), если иное не указано в данном задании. Требование к оборудованию охранного телевидения Требования к камерам Модель/количество видеокамер: Внутренняя IP-видеокамера Dahua DH-IPC-HDW3449HP-AS-PV-0280B-PRO</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Источник: 851900595.txt</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/vse-loti/339193000/spec-339193000.xlsx
+++ b/vse-loti/339193000/spec-339193000.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +440,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,7 +511,7 @@
           <t>комплект со склада СОТ (шкаф, ИБП с картой мониторинга, АВР – новые на складе СОТ), смонтировать по проекту с переносом линий. Доукомплектовать шкаф «грозозацитой SNR-SPNet-PRM24-v2» и 3 модулями «Грозозащита Ethernet SNR-SPNet-BP1100», патч панелью ( cabeus 7955 c + 7962 c или аналог) (Приложение 2 ) . Видеокамеру CAM-66-ST подключить с использование POE удлинителя. POE удлинитель разместить в боксе, в доступном месте, на высоте 1,5 м. Предусмотреть доукомплектование узлов связи N узла ИБП (оборудование Заказчика) Грозозащита SNR-SPNet-PRM24-v2» и модули Ethernet SNR-SPNet-BP1100» (оборудование Подрядчика) Патч панель (cabeus 7955c + 7962c или аналог) (оборудование Подрядчика) N01 + N02 + + + N04 + + + N10 + + + Требования к архитектурно-строительным, объемно-планировочным и конструктивным решениям Не требуется Требования к режиму безопасности и гигиене труда Технические решения должны соответствовать требованиям экономических, санитарно-гигиенических, противопожарных и других норм, действующих на территории Российской Федерации, и обеспечивать безопасную для жизни и здоровья людей эксплуатацию объекта. Устанавливаемое на объекте оборудование должно быть безвредно для здоровья лиц, имеющих доступ на объект. Требования и условия для разработки природоохранных мер и мероприятий Не требуется . Требования по разработке инженерно-технических мероприятий по гражданской обороне и предупреждению чрезвычайных ситуаций Не требуется . Требования по выполнению исследований и конструкторских разработок Не требуется . Требования к проведению, оформлению и представлению расчета стоимости строительства Локально сметный расчет выполнить ресурсно-индексным методом в федеральной сметно-нормативной базе ФСНБ 2022 г. Для материалов отсутствующих в сметно-нормативной базе, в расчете предоставить конъюнктурный анализ с предоставлением не менее трех прайсов на каждую позицию материалов поставщиков Челябинской области. Особые условия Не требуются . Перечень технических регламентов и стандартов, норм и правил, соответствие которым необходимо обеспечить при проектировании ГОСТ Р 21.1101-20 20 СПДС. Основные требования к проектной и рабочей документации (с Поправкой) ГОСТ Р 21.101-2020 СПДС. Спецификация оборудования, изделий и материалов. ГОСТ Р 53246-2008 Информационные технологии (ИТ). Системы кабельные структурированные. Проектирование основных узлов системы. Общие требования. ГОСТ Р 53245-2008. Информационные технологии. Системы кабельные структурированные. Монтаж основных узлов системы. Методы испытания. Правила по охране труда при эксплуатации электроустановок Правила по охране труда при выполнении работ на объектах связи Перечень согласований и экспертиз в государственных федеральных и региональных надзорных органах Не требуется . Требования к процедуре подтверждения соответствия проекта Заданию на проектирование Внутренняя экспертиза Заказчика (ПСД и проектных решений) . Требования к телекоммуникационной инфраструктуре Для подключения проектируемого объекта к сети передачи данных запросить технические условия в управлении ИТ филиала ПАО «ТМК» ЧТПЗ на этапе проектирования. Проектирование и строительство объекта выполнить в соответствии с типовыми требованиями ИТ к телекоммуникационной инфраструктуре. (приложение 3 ), если иное не указано в данном задании. Требование к оборудованию охранного телевидения Требования к камерам Модель/количество видеокамер: Внутренняя IP-видеокамера Dahua DH-IPC-HDW3449HP-AS-PV-0280B-PRO</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -514,25 +520,25 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/vse-loti/339193000/spec-339193000.xlsx
+++ b/vse-loti/339193000/spec-339193000.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -61,15 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -446,8 +441,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,25 +471,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -520,26 +503,14 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
